--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.167.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.167.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -875,7 +875,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.167.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.167.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -595,22 +595,26 @@
       <c r="G2" s="1" t="inlineStr"/>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITyâ€”Continued.</t>
+          <t>L1: suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITy—Continued.</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L1: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): EQuITy (odd internal casing) :: BILL IN EQuITyâ€”Continued.</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BILL IN Equityâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]160</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]160</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L12: isolated marker/symbol line :: 160</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L19: isolated marker/symbol line :: E</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]160</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 46â€”47</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L23: isolated marker/symbol line :: S</t>
+          <t>L19: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -731,12 +735,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 115 â€” 116</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L35: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Whether dismissal of Bill a Bar to another suit . 70â€”71</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -748,7 +752,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L24: isolated marker/symbol line :: 0</t>
+          <t>L23: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -770,12 +774,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>45</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -786,12 +790,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L62: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸Š</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -803,7 +807,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L25: isolated marker/symbol line :: T</t>
+          <t>L24: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -841,14 +845,10 @@
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 115â€”116</t>
-        </is>
-      </c>
+          <t>L96: stray/suspicious non-ASCII glyph(s): U+6B63 CJK UNIFIED IDEOGRAPH-6B63 | isolated marker/symbol line :: 正</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 23</t>
+          <t>L25: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -896,24 +896,20 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 7 â€” 10</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L91: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Orders. (See" Speeding the Cause.") 70â€”71â€”72</t>
-        </is>
-      </c>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 20</t>
+          <t>L27: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -949,16 +945,8 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: æ­£</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 69â€”70</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -968,7 +956,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: 24</t>
+          <t>L29: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1004,26 +992,18 @@
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L105: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 111â€”112</t>
-        </is>
-      </c>
+      <c r="J9" s="1" t="inlineStr"/>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L26: isolated marker/symbol line :: E</t>
+          <t>L23: symbol-only separator/garbage line :: 115 — 116</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 0</t>
+          <t>L30: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1045,12 +1025,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1060,21 +1040,17 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L28: isolated marker/symbol line :: S</t>
+          <t>L26: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: S</t>
+          <t>L32: symbol-only separator/garbage line :: 46—47</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1101,7 +1077,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1111,21 +1087,17 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: Cases in which/the Court gives Relief .â€˜</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 0</t>
+          <t>L28: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: I</t>
+          <t>L45: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1147,12 +1119,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
           <t>43</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1162,21 +1134,17 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L145: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 7â€”10</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: T</t>
+          <t>L29: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: C</t>
+          <t>L49: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1213,21 +1181,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L31: isolated marker/symbol line :: O</t>
+          <t>L30: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: C</t>
+          <t>L51: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1269,12 +1233,12 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L32: isolated marker/symbol line :: 0</t>
+          <t>L31: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L54: isolated marker/symbol line :: C</t>
+          <t>L52: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1316,12 +1280,12 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: M</t>
+          <t>L32: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: A</t>
+          <t>L53: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1363,12 +1327,12 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: S</t>
+          <t>L34: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: I</t>
+          <t>L54: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1410,12 +1374,12 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: t</t>
+          <t>L35: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: s</t>
+          <t>L55: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1445,12 +1409,12 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L52: isolated marker/symbol line :: S</t>
+          <t>L37: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: z</t>
+          <t>L57: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1480,12 +1444,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L55: symbol-only separator/garbage line :: 69-70</t>
+          <t>L52: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L58: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1515,12 +1479,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 108</t>
+          <t>L55: symbol-only separator/garbage line :: 69-70</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: s</t>
+          <t>L61: isolated marker/symbol line :: z</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1550,12 +1514,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 109</t>
+          <t>L57: isolated marker/symbol line :: 108</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: I</t>
+          <t>L64: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1585,12 +1549,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L59: symbol-only separator/garbage line :: 111-112</t>
+          <t>L58: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 1</t>
+          <t>L65: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1620,12 +1584,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 116</t>
+          <t>L59: symbol-only separator/garbage line :: 111-112</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: I</t>
+          <t>L66: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1655,12 +1619,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: F</t>
+          <t>L60: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: I</t>
+          <t>L67: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1690,12 +1654,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 1</t>
+          <t>L61: isolated marker/symbol line :: F</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L75: isolated marker/symbol line :: ]</t>
+          <t>L69: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1725,12 +1689,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: S</t>
+          <t>L62: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L101: symbol-only separator/garbage line :: . 108</t>
+          <t>L72: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1760,12 +1724,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: P</t>
+          <t>L63: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 109</t>
+          <t>L75: isolated marker/symbol line :: ]</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1795,12 +1759,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: 4</t>
+          <t>L64: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L77: symbol-only separator/garbage line :: . 115—116</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1830,12 +1794,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: B</t>
+          <t>L66: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: -</t>
+          <t>L99: symbol-only separator/garbage line :: 69—70</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1865,12 +1829,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 2</t>
+          <t>L68: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 116</t>
+          <t>L101: symbol-only separator/garbage line :: . 108</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1900,12 +1864,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L82: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L74: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: .2</t>
+          <t>L103: isolated marker/symbol line :: 109</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1935,12 +1899,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 7</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: 7</t>
+          <t>L105: symbol-only separator/garbage line :: . 111—112</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1970,12 +1934,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 10</t>
+          <t>L81: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L149: symbol-only separator/garbage line :: .10</t>
+          <t>L107: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2005,12 +1969,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 12</t>
+          <t>L82: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L153: symbol-only separator/garbage line :: .12</t>
+          <t>L109: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2040,12 +2004,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 10</t>
+          <t>L86: symbol-only separator/garbage line :: . 7 — 10</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L137: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2075,12 +2039,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 7</t>
+          <t>L87: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: ]</t>
+          <t>L139: isolated marker/symbol line :: .2</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2110,12 +2074,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 02</t>
+          <t>L88: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L159: isolated marker/symbol line :: 10</t>
+          <t>L145: symbol-only separator/garbage line :: . 7—10</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2145,12 +2109,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 1</t>
+          <t>L91: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L160: isolated marker/symbol line :: .7</t>
+          <t>L147: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2180,10 +2144,14 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+00AD SOFT HYPHEN | isolated marker/symbol line :: æ­£</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr"/>
+          <t>L92: isolated marker/symbol line :: 10</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>L149: symbol-only separator/garbage line :: .10</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2211,10 +2179,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: 1</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L93: isolated marker/symbol line :: 7</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L153: symbol-only separator/garbage line :: .12</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2242,10 +2214,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L94: isolated marker/symbol line :: 02</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L155: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2273,10 +2249,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: T</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L95: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L157: isolated marker/symbol line :: ]</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2304,10 +2284,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L96: stray/suspicious non-ASCII glyph(s): U+6B63 CJK UNIFIED IDEOGRAPH-6B63 | isolated marker/symbol line :: 正</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L159: isolated marker/symbol line :: 10</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2335,10 +2319,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: H</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L97: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L160: isolated marker/symbol line :: .7</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2350,6 +2338,130 @@
       <c r="X44" s="1" t="inlineStr"/>
       <c r="Y44" s="1" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr"/>
+      <c r="B45" s="1" t="inlineStr"/>
+      <c r="C45" s="1" t="inlineStr"/>
+      <c r="D45" s="1" t="inlineStr"/>
+      <c r="E45" s="1" t="inlineStr"/>
+      <c r="F45" s="1" t="inlineStr"/>
+      <c r="G45" s="1" t="inlineStr"/>
+      <c r="H45" s="1" t="inlineStr"/>
+      <c r="I45" s="1" t="inlineStr"/>
+      <c r="J45" s="1" t="inlineStr"/>
+      <c r="K45" s="1" t="inlineStr"/>
+      <c r="L45" s="1" t="inlineStr"/>
+      <c r="M45" s="1" t="inlineStr"/>
+      <c r="N45" s="1" t="inlineStr">
+        <is>
+          <t>L98: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O45" s="1" t="inlineStr"/>
+      <c r="P45" s="1" t="inlineStr"/>
+      <c r="Q45" s="1" t="inlineStr"/>
+      <c r="R45" s="1" t="inlineStr"/>
+      <c r="S45" s="1" t="inlineStr"/>
+      <c r="T45" s="1" t="inlineStr"/>
+      <c r="U45" s="1" t="inlineStr"/>
+      <c r="V45" s="1" t="inlineStr"/>
+      <c r="W45" s="1" t="inlineStr"/>
+      <c r="X45" s="1" t="inlineStr"/>
+      <c r="Y45" s="1" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr"/>
+      <c r="B46" s="1" t="inlineStr"/>
+      <c r="C46" s="1" t="inlineStr"/>
+      <c r="D46" s="1" t="inlineStr"/>
+      <c r="E46" s="1" t="inlineStr"/>
+      <c r="F46" s="1" t="inlineStr"/>
+      <c r="G46" s="1" t="inlineStr"/>
+      <c r="H46" s="1" t="inlineStr"/>
+      <c r="I46" s="1" t="inlineStr"/>
+      <c r="J46" s="1" t="inlineStr"/>
+      <c r="K46" s="1" t="inlineStr"/>
+      <c r="L46" s="1" t="inlineStr"/>
+      <c r="M46" s="1" t="inlineStr"/>
+      <c r="N46" s="1" t="inlineStr">
+        <is>
+          <t>L99: isolated marker/symbol line :: T</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="inlineStr"/>
+      <c r="P46" s="1" t="inlineStr"/>
+      <c r="Q46" s="1" t="inlineStr"/>
+      <c r="R46" s="1" t="inlineStr"/>
+      <c r="S46" s="1" t="inlineStr"/>
+      <c r="T46" s="1" t="inlineStr"/>
+      <c r="U46" s="1" t="inlineStr"/>
+      <c r="V46" s="1" t="inlineStr"/>
+      <c r="W46" s="1" t="inlineStr"/>
+      <c r="X46" s="1" t="inlineStr"/>
+      <c r="Y46" s="1" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr"/>
+      <c r="B47" s="1" t="inlineStr"/>
+      <c r="C47" s="1" t="inlineStr"/>
+      <c r="D47" s="1" t="inlineStr"/>
+      <c r="E47" s="1" t="inlineStr"/>
+      <c r="F47" s="1" t="inlineStr"/>
+      <c r="G47" s="1" t="inlineStr"/>
+      <c r="H47" s="1" t="inlineStr"/>
+      <c r="I47" s="1" t="inlineStr"/>
+      <c r="J47" s="1" t="inlineStr"/>
+      <c r="K47" s="1" t="inlineStr"/>
+      <c r="L47" s="1" t="inlineStr"/>
+      <c r="M47" s="1" t="inlineStr"/>
+      <c r="N47" s="1" t="inlineStr">
+        <is>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O47" s="1" t="inlineStr"/>
+      <c r="P47" s="1" t="inlineStr"/>
+      <c r="Q47" s="1" t="inlineStr"/>
+      <c r="R47" s="1" t="inlineStr"/>
+      <c r="S47" s="1" t="inlineStr"/>
+      <c r="T47" s="1" t="inlineStr"/>
+      <c r="U47" s="1" t="inlineStr"/>
+      <c r="V47" s="1" t="inlineStr"/>
+      <c r="W47" s="1" t="inlineStr"/>
+      <c r="X47" s="1" t="inlineStr"/>
+      <c r="Y47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr"/>
+      <c r="B48" s="1" t="inlineStr"/>
+      <c r="C48" s="1" t="inlineStr"/>
+      <c r="D48" s="1" t="inlineStr"/>
+      <c r="E48" s="1" t="inlineStr"/>
+      <c r="F48" s="1" t="inlineStr"/>
+      <c r="G48" s="1" t="inlineStr"/>
+      <c r="H48" s="1" t="inlineStr"/>
+      <c r="I48" s="1" t="inlineStr"/>
+      <c r="J48" s="1" t="inlineStr"/>
+      <c r="K48" s="1" t="inlineStr"/>
+      <c r="L48" s="1" t="inlineStr"/>
+      <c r="M48" s="1" t="inlineStr"/>
+      <c r="N48" s="1" t="inlineStr">
+        <is>
+          <t>L102: isolated marker/symbol line :: H</t>
+        </is>
+      </c>
+      <c r="O48" s="1" t="inlineStr"/>
+      <c r="P48" s="1" t="inlineStr"/>
+      <c r="Q48" s="1" t="inlineStr"/>
+      <c r="R48" s="1" t="inlineStr"/>
+      <c r="S48" s="1" t="inlineStr"/>
+      <c r="T48" s="1" t="inlineStr"/>
+      <c r="U48" s="1" t="inlineStr"/>
+      <c r="V48" s="1" t="inlineStr"/>
+      <c r="W48" s="1" t="inlineStr"/>
+      <c r="X48" s="1" t="inlineStr"/>
+      <c r="Y48" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
